--- a/research/traditional_assets/database/data/luxembourg/luxembourg_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,109 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.3885</v>
+        <v>0.101</v>
       </c>
       <c r="E2">
-        <v>0.1478</v>
+        <v>0.0973</v>
       </c>
       <c r="G2">
-        <v>0.09434030804998546</v>
+        <v>0.4708481824661439</v>
       </c>
       <c r="H2">
-        <v>0.09434030804998546</v>
+        <v>0.4708481824661439</v>
       </c>
       <c r="I2">
-        <v>1.000871839581517</v>
+        <v>0.9821019244476124</v>
       </c>
       <c r="J2">
-        <v>0.9916745350763249</v>
+        <v>0.978785476730154</v>
       </c>
       <c r="K2">
-        <v>2053.6</v>
+        <v>1472.419</v>
       </c>
       <c r="L2">
-        <v>0.7460040685847137</v>
+        <v>1.04947897362794</v>
       </c>
       <c r="M2">
-        <v>190.347</v>
+        <v>231.569</v>
       </c>
       <c r="N2">
-        <v>0.01691702660907588</v>
+        <v>0.02157300963276257</v>
       </c>
       <c r="O2">
-        <v>0.0926894234514998</v>
+        <v>0.1572711300248096</v>
       </c>
       <c r="P2">
-        <v>190.2</v>
+        <v>183.5</v>
       </c>
       <c r="Q2">
-        <v>0.01690396203274143</v>
+        <v>0.01709489295895363</v>
       </c>
       <c r="R2">
-        <v>0.09261784183872224</v>
+        <v>0.1246248520292118</v>
       </c>
       <c r="S2">
-        <v>0.1469999999999985</v>
+        <v>48.069</v>
       </c>
       <c r="T2">
-        <v>0.0007722737947012481</v>
+        <v>0.2075795983054727</v>
       </c>
       <c r="U2">
-        <v>186.973</v>
+        <v>277.006</v>
       </c>
       <c r="V2">
-        <v>0.01661716347606605</v>
-      </c>
-      <c r="W2">
-        <v>0.1093394077448747</v>
+        <v>0.02580592871383056</v>
       </c>
       <c r="X2">
-        <v>0.04388745577896895</v>
-      </c>
-      <c r="Y2">
-        <v>0.06545195196590577</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Z2">
-        <v>0.255032698994155</v>
-      </c>
-      <c r="AA2">
-        <v>0.1908038493773946</v>
+        <v>0.1086994670472104</v>
       </c>
       <c r="AB2">
-        <v>0.0438697773553725</v>
-      </c>
-      <c r="AC2">
-        <v>0.1469340720220221</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD2">
-        <v>74.92</v>
+        <v>164.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>74.92</v>
+        <v>164.4</v>
       </c>
       <c r="AG2">
-        <v>-112.053</v>
+        <v>-112.606</v>
       </c>
       <c r="AH2">
-        <v>0.006614447960221493</v>
+        <v>0.01508450626685996</v>
       </c>
       <c r="AI2">
-        <v>0.005629814874373672</v>
+        <v>0.01295588929492065</v>
       </c>
       <c r="AJ2">
-        <v>-0.01005884604021976</v>
+        <v>-0.01060161026678293</v>
       </c>
       <c r="AK2">
-        <v>-0.008540138758867923</v>
+        <v>-0.009072200231320725</v>
       </c>
       <c r="AL2">
-        <v>2.684</v>
+        <v>7.225000000000001</v>
       </c>
       <c r="AM2">
-        <v>1.697</v>
+        <v>6.732</v>
       </c>
       <c r="AN2">
-        <v>0.1137737281700835</v>
+        <v>0.4136889783593357</v>
       </c>
       <c r="AO2">
-        <v>1026.527570789866</v>
+        <v>190.7112802768166</v>
       </c>
       <c r="AP2">
-        <v>-0.1701640091116173</v>
+        <v>-0.2833568193256166</v>
       </c>
       <c r="AQ2">
-        <v>1623.571007660577</v>
+        <v>204.6775103980986</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brederode SA (ENXTBR:BREB)</t>
+          <t>BBGI Global Infrastructure S.A. (LSE:BBGI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +710,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.638</v>
+        <v>0.179</v>
       </c>
       <c r="E3">
-        <v>0.653</v>
+        <v>0.162</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.4373795761078998</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.4373795761078998</v>
       </c>
       <c r="I3">
-        <v>1.037160505931954</v>
+        <v>0.8636801541425819</v>
       </c>
       <c r="J3">
-        <v>1.037160505931954</v>
+        <v>0.8464952473528387</v>
       </c>
       <c r="K3">
-        <v>1057.8</v>
+        <v>152.7</v>
       </c>
       <c r="L3">
-        <v>1.037160505931954</v>
+        <v>0.7355491329479769</v>
       </c>
       <c r="M3">
-        <v>37.5</v>
+        <v>60.4</v>
       </c>
       <c r="N3">
-        <v>0.009181499889822002</v>
+        <v>0.04487369985141159</v>
       </c>
       <c r="O3">
-        <v>0.03545093590470789</v>
+        <v>0.39554682383759</v>
       </c>
       <c r="P3">
-        <v>37.5</v>
+        <v>60.4</v>
       </c>
       <c r="Q3">
-        <v>0.009181499889822002</v>
+        <v>0.04487369985141159</v>
       </c>
       <c r="R3">
-        <v>0.03545093590470789</v>
+        <v>0.39554682383759</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,61 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.213</v>
+        <v>48.8</v>
       </c>
       <c r="V3">
-        <v>5.215091937418896e-05</v>
+        <v>0.0362555720653789</v>
       </c>
       <c r="W3">
-        <v>0.3941279481351764</v>
+        <v>0.1204258675078864</v>
       </c>
       <c r="X3">
-        <v>0.04387296409148227</v>
+        <v>0.07265878318576451</v>
       </c>
       <c r="Y3">
-        <v>0.3502549840436941</v>
+        <v>0.04776708432212193</v>
       </c>
       <c r="Z3">
-        <v>0.3800194499610628</v>
+        <v>0.1648534900341459</v>
       </c>
       <c r="AA3">
-        <v>0.3941411649855988</v>
+        <v>0.1395476958234331</v>
       </c>
       <c r="AB3">
-        <v>0.04387296409148227</v>
+        <v>0.07236031322134205</v>
       </c>
       <c r="AC3">
-        <v>0.3502682008941165</v>
+        <v>0.06718738260209102</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="AG3">
-        <v>-0.213</v>
+        <v>-37.9</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.008033016434519862</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.008323787705231005</v>
       </c>
       <c r="AJ3">
-        <v>-5.215363923442375e-05</v>
+        <v>-0.0289733200825625</v>
       </c>
       <c r="AK3">
-        <v>-5.535649452529467e-05</v>
+        <v>-0.03006266359958753</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>2.403</v>
+      </c>
+      <c r="AN3">
+        <v>0.06075808249721294</v>
+      </c>
+      <c r="AO3">
+        <v>74.39834024896265</v>
+      </c>
+      <c r="AP3">
+        <v>-0.2112597547380156</v>
+      </c>
+      <c r="AQ3">
+        <v>74.61506450270495</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Luxempart S.A. (BDL:LXMPR)</t>
+          <t>Reinet Investments S.C.A. (BDL:REINI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -843,122 +843,104 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.6709999999999999</v>
-      </c>
-      <c r="E4">
-        <v>0.352</v>
-      </c>
       <c r="G4">
-        <v>0.3161898462047296</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.3161898462047296</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.9720522573176781</v>
+        <v>0.9934902353530296</v>
       </c>
       <c r="J4">
-        <v>0.9720109355927454</v>
+        <v>0.9934902353530296</v>
       </c>
       <c r="K4">
-        <v>588.1</v>
+        <v>744.3</v>
       </c>
       <c r="L4">
-        <v>0.972548371093104</v>
+        <v>1.242363545317977</v>
       </c>
       <c r="M4">
-        <v>38.247</v>
+        <v>98</v>
       </c>
       <c r="N4">
-        <v>0.02245332863684396</v>
+        <v>0.02833762253130151</v>
       </c>
       <c r="O4">
-        <v>0.06503485801734399</v>
+        <v>0.1316673384388016</v>
       </c>
       <c r="P4">
-        <v>38.1</v>
+        <v>50</v>
       </c>
       <c r="Q4">
-        <v>0.02236703064459317</v>
+        <v>0.01445797067923546</v>
       </c>
       <c r="R4">
-        <v>0.06478490052712124</v>
+        <v>0.06717721348918447</v>
       </c>
       <c r="S4">
-        <v>0.1469999999999985</v>
+        <v>48</v>
       </c>
       <c r="T4">
-        <v>0.003843438701074554</v>
+        <v>0.4897959183673469</v>
       </c>
       <c r="U4">
-        <v>46.3</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.02718093225314077</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>0.3617963703475854</v>
+        <v>0.1342920034642032</v>
       </c>
       <c r="X4">
-        <v>0.04438264993817247</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y4">
-        <v>0.3174137204094129</v>
+        <v>0.06183778442349837</v>
       </c>
       <c r="Z4">
-        <v>0.3794791339818011</v>
+        <v>0.1080713476538542</v>
       </c>
       <c r="AA4">
-        <v>0.3688578680595752</v>
+        <v>0.1073678286155467</v>
       </c>
       <c r="AB4">
-        <v>0.04376339430528924</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC4">
-        <v>0.325094473754286</v>
+        <v>0.03491360957484185</v>
       </c>
       <c r="AD4">
-        <v>40.2</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>40.2</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-6.099999999999994</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>0.02305574673090158</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.01745700885878062</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.003593943321746299</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>-0.00270330157323288</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>0.454</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.5269999999999999</v>
-      </c>
-      <c r="AN4">
-        <v>0.06836734693877551</v>
-      </c>
-      <c r="AO4">
-        <v>1294.713656387665</v>
-      </c>
-      <c r="AP4">
-        <v>-0.01037414965986394</v>
-      </c>
-      <c r="AQ4">
-        <v>-1115.370018975332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reinet Investments S.C.A. (BDL:REINI)</t>
+          <t>Brederode SA (ENXTBR:BREB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,10 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.139</v>
+        <v>0.101</v>
       </c>
       <c r="E5">
-        <v>-0.09570000000000001</v>
+        <v>0.0965</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,34 +972,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.9976523525383938</v>
+        <v>1.086703601108033</v>
       </c>
       <c r="J5">
-        <v>0.9976523525383938</v>
+        <v>1.086703601108033</v>
       </c>
       <c r="K5">
-        <v>321</v>
+        <v>392.3</v>
       </c>
       <c r="L5">
-        <v>0.3139978479898269</v>
+        <v>1.086703601108033</v>
       </c>
       <c r="M5">
-        <v>53.3</v>
+        <v>35.2</v>
       </c>
       <c r="N5">
-        <v>0.01541576283441793</v>
+        <v>0.01079258010118044</v>
       </c>
       <c r="O5">
-        <v>0.1660436137071651</v>
+        <v>0.08972724955391283</v>
       </c>
       <c r="P5">
-        <v>53.3</v>
+        <v>35.2</v>
       </c>
       <c r="Q5">
-        <v>0.01541576283441793</v>
+        <v>0.01079258010118044</v>
       </c>
       <c r="R5">
-        <v>0.1660436137071651</v>
+        <v>0.08972724955391283</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1026,55 +1008,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1.16</v>
+        <v>0.125</v>
       </c>
       <c r="V5">
-        <v>0.0003355025307302964</v>
+        <v>3.832592365476008e-05</v>
       </c>
       <c r="W5">
-        <v>0.06006624127542523</v>
+        <v>0.1019490644490645</v>
       </c>
       <c r="X5">
-        <v>0.04388745577896895</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y5">
-        <v>0.01617878549645628</v>
+        <v>0.0294948454083596</v>
       </c>
       <c r="Z5">
-        <v>0.1912528436302682</v>
+        <v>0.09382016208277641</v>
       </c>
       <c r="AA5">
-        <v>0.1908038493773946</v>
+        <v>0.1019547079918925</v>
       </c>
       <c r="AB5">
-        <v>0.0438697773553725</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC5">
-        <v>0.1469340720220221</v>
+        <v>0.02950048895118763</v>
       </c>
       <c r="AD5">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>1.16</v>
+        <v>-0.125</v>
       </c>
       <c r="AH5">
-        <v>0.0006705551155840476</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.0004184160787199354</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.0003353900065343225</v>
+        <v>-3.832739258748227e-05</v>
       </c>
       <c r="AK5">
-        <v>0.0002092518165222348</v>
+        <v>-3.333711153930779e-05</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1091,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NB Aurora S.A. SICAF-RAIF (BIT:NBA)</t>
+          <t>Luxempart S.A. (BDL:LXMPR)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1099,71 +1081,80 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.0269</v>
+      </c>
+      <c r="E6">
+        <v>0.0973</v>
+      </c>
       <c r="G6">
-        <v>0</v>
+        <v>2.421589460263493</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2.421589460263493</v>
       </c>
       <c r="I6">
-        <v>0.7966804979253111</v>
+        <v>0.9260518487037824</v>
       </c>
       <c r="J6">
-        <v>0.7966804979253111</v>
+        <v>0.9163332278227949</v>
       </c>
       <c r="K6">
-        <v>19.2</v>
+        <v>214.1</v>
       </c>
       <c r="L6">
-        <v>0.7966804979253111</v>
+        <v>0.9099022524436888</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>37.969</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.02366406980367716</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.1773423633815974</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>37.9</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.02362106575257089</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.1770200840728632</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.06900000000000261</v>
+      </c>
+      <c r="T6">
+        <v>0.001817271985040497</v>
       </c>
       <c r="U6">
-        <v>98.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="V6">
-        <v>0.3133375877472878</v>
+        <v>0.04543471486444375</v>
       </c>
       <c r="W6">
-        <v>0.1093394077448747</v>
+        <v>0.09462565190488818</v>
       </c>
       <c r="X6">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y6">
-        <v>0.06546644365339244</v>
+        <v>0.02217143286418333</v>
       </c>
       <c r="Z6">
-        <v>0.201000834028357</v>
+        <v>0.104276534456016</v>
       </c>
       <c r="AA6">
-        <v>0.1601334445371143</v>
+        <v>0.09555205340425602</v>
       </c>
       <c r="AB6">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC6">
-        <v>0.116260480445632</v>
+        <v>0.02309783436355116</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1175,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-98.2</v>
+        <v>-72.90000000000001</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1184,19 +1175,28 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.4563197026022305</v>
+        <v>-0.04759728388613216</v>
       </c>
       <c r="AK6">
-        <v>-0.4597378277153558</v>
+        <v>-0.03473247891752823</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.963</v>
       </c>
       <c r="AM6">
-        <v>-0.006</v>
+        <v>0.477</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>226.2720664589824</v>
+      </c>
+      <c r="AP6">
+        <v>-0.3344036697247706</v>
       </c>
       <c r="AQ6">
-        <v>-3200</v>
+        <v>456.8134171907757</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BBGI Global Infrastructure S.A. (LSE:BBGI)</t>
+          <t>468 SPAC II SE (DB:SPV2)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1215,122 +1215,427 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D7">
-        <v>-0.0555</v>
-      </c>
-      <c r="E7">
-        <v>-0.0564</v>
-      </c>
-      <c r="G7">
-        <v>0.8374083129584352</v>
-      </c>
-      <c r="H7">
-        <v>0.8374083129584352</v>
-      </c>
-      <c r="I7">
-        <v>0.8618581907090465</v>
-      </c>
-      <c r="J7">
-        <v>0.8222954912767809</v>
-      </c>
       <c r="K7">
-        <v>67.5</v>
-      </c>
-      <c r="L7">
-        <v>0.8251833740831296</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="M7">
-        <v>61.3</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.03620363808173872</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.9081481481481481</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>61.3</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.03620363808173872</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.9081481481481481</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>41.1</v>
+        <v>3.64</v>
       </c>
       <c r="V7">
-        <v>0.0242735648476258</v>
-      </c>
-      <c r="W7">
-        <v>0.06355333772714435</v>
+        <v>0.01360239162929746</v>
       </c>
       <c r="X7">
-        <v>0.0442862303174715</v>
-      </c>
-      <c r="Y7">
-        <v>0.01926710740967284</v>
-      </c>
-      <c r="Z7">
-        <v>0.07779954727891804</v>
-      </c>
-      <c r="AA7">
-        <v>0.06397421695082905</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AB7">
-        <v>0.04378373293954781</v>
-      </c>
-      <c r="AC7">
-        <v>0.02019048401128125</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD7">
-        <v>32.4</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>32.4</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>-8.700000000000003</v>
+        <v>-3.64</v>
       </c>
       <c r="AH7">
-        <v>0.01877607788595271</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.02491541064287911</v>
+        <v>-0</v>
       </c>
       <c r="AJ7">
-        <v>-0.005164737310774712</v>
+        <v>-0.01378996817699651</v>
       </c>
       <c r="AK7">
-        <v>-0.006908600015881842</v>
+        <v>0.3466666666666667</v>
       </c>
       <c r="AL7">
-        <v>2.23</v>
+        <v>0.001</v>
       </c>
       <c r="AM7">
-        <v>2.23</v>
-      </c>
-      <c r="AN7">
-        <v>0.4595744680851064</v>
+        <v>0.001</v>
       </c>
       <c r="AO7">
-        <v>31.61434977578475</v>
-      </c>
-      <c r="AP7">
-        <v>-0.123404255319149</v>
+        <v>-564.9999999999999</v>
       </c>
       <c r="AQ7">
-        <v>31.61434977578475</v>
+        <v>-564.9999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OboTech Acquisition SE (DB:OTA)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K8">
+        <v>-11</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>2.05</v>
+      </c>
+      <c r="V8">
+        <v>0.007768093974990527</v>
+      </c>
+      <c r="X8">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AB8">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>-2.05</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>-0</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.007828909681115142</v>
+      </c>
+      <c r="AK8">
+        <v>0.1734348561759729</v>
+      </c>
+      <c r="AL8">
+        <v>3.81</v>
+      </c>
+      <c r="AM8">
+        <v>3.81</v>
+      </c>
+      <c r="AO8">
+        <v>-0.5013123359580052</v>
+      </c>
+      <c r="AQ8">
+        <v>-0.5013123359580052</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GFJ ESG Acquisition I SE (DB:GFJ1)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K9">
+        <v>-16.8</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0.131</v>
+      </c>
+      <c r="V9">
+        <v>0.0006569709127382146</v>
+      </c>
+      <c r="X9">
+        <v>0.09190026478110001</v>
+      </c>
+      <c r="AB9">
+        <v>0.07112405292533676</v>
+      </c>
+      <c r="AD9">
+        <v>153.5</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>153.5</v>
+      </c>
+      <c r="AG9">
+        <v>153.369</v>
+      </c>
+      <c r="AH9">
+        <v>0.4349674128648343</v>
+      </c>
+      <c r="AI9">
+        <v>1.083274523641496</v>
+      </c>
+      <c r="AJ9">
+        <v>0.4347575892439529</v>
+      </c>
+      <c r="AK9">
+        <v>1.08335158120775</v>
+      </c>
+      <c r="AL9">
+        <v>0.04</v>
+      </c>
+      <c r="AM9">
+        <v>0.04</v>
+      </c>
+      <c r="AO9">
+        <v>-43</v>
+      </c>
+      <c r="AQ9">
+        <v>-43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hiro Metaverse Acquisitions I S.A. (LSE:HMA1)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K10">
+        <v>-0.825</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>146.8</v>
+      </c>
+      <c r="V10">
+        <v>0.8256467941507312</v>
+      </c>
+      <c r="X10">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AB10">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>-146.8</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>-4.735483870967743</v>
+      </c>
+      <c r="AK10">
+        <v>1.002458344714559</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SMG European Recovery SPAC SE (DB:RCVR)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K11">
+        <v>-1.79</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>2.56</v>
+      </c>
+      <c r="V11">
+        <v>0.01649484536082474</v>
+      </c>
+      <c r="X11">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AB11">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>-2.56</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>-0</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.01677148846960168</v>
+      </c>
+      <c r="AK11">
+        <v>0.4942084942084942</v>
+      </c>
+      <c r="AL11">
+        <v>0.001</v>
+      </c>
+      <c r="AM11">
+        <v>0.001</v>
+      </c>
+      <c r="AO11">
+        <v>-1790</v>
+      </c>
+      <c r="AQ11">
+        <v>-1790</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,109 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.101</v>
+        <v>-0.08560000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0973</v>
+        <v>-0.0828</v>
       </c>
       <c r="G2">
-        <v>0.4708481824661439</v>
+        <v>0.4609625668449198</v>
       </c>
       <c r="H2">
-        <v>0.4708481824661439</v>
+        <v>0.4609625668449198</v>
       </c>
       <c r="I2">
-        <v>0.9821019244476124</v>
+        <v>0.7217112299465241</v>
       </c>
       <c r="J2">
-        <v>0.978785476730154</v>
+        <v>0.7044518896252518</v>
       </c>
       <c r="K2">
-        <v>1472.419</v>
+        <v>708</v>
       </c>
       <c r="L2">
-        <v>1.04947897362794</v>
+        <v>1.514438502673797</v>
       </c>
       <c r="M2">
-        <v>231.569</v>
+        <v>207.322</v>
       </c>
       <c r="N2">
-        <v>0.02157300963276257</v>
+        <v>0.01901042574066772</v>
       </c>
       <c r="O2">
-        <v>0.1572711300248096</v>
+        <v>0.2928276836158192</v>
       </c>
       <c r="P2">
-        <v>183.5</v>
+        <v>206.5</v>
       </c>
       <c r="Q2">
-        <v>0.01709489295895363</v>
+        <v>0.01893505231209367</v>
       </c>
       <c r="R2">
-        <v>0.1246248520292118</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="S2">
-        <v>48.069</v>
+        <v>0.8220000000000027</v>
       </c>
       <c r="T2">
-        <v>0.2075795983054727</v>
+        <v>0.003964846953048893</v>
       </c>
       <c r="U2">
-        <v>277.006</v>
+        <v>77.355</v>
       </c>
       <c r="V2">
-        <v>0.02580592871383056</v>
+        <v>0.007093079765627149</v>
+      </c>
+      <c r="W2">
+        <v>0.04808384670773663</v>
       </c>
       <c r="X2">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="Y2">
+        <v>-0.01422454182806501</v>
       </c>
       <c r="Z2">
-        <v>0.1086994670472104</v>
+        <v>0.03676940470923659</v>
+      </c>
+      <c r="AA2">
+        <v>0.04810918408061104</v>
       </c>
       <c r="AB2">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="AC2">
+        <v>-0.01419920445519059</v>
       </c>
       <c r="AD2">
-        <v>164.4</v>
+        <v>31.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>164.4</v>
+        <v>31.8</v>
       </c>
       <c r="AG2">
-        <v>-112.606</v>
+        <v>-45.55500000000001</v>
       </c>
       <c r="AH2">
-        <v>0.01508450626685996</v>
+        <v>0.002907428571428572</v>
       </c>
       <c r="AI2">
-        <v>0.01295588929492065</v>
+        <v>0.002245318722286554</v>
       </c>
       <c r="AJ2">
-        <v>-0.01060161026678293</v>
+        <v>-0.004194695374693433</v>
       </c>
       <c r="AK2">
-        <v>-0.009072200231320725</v>
+        <v>-0.003234189619142314</v>
       </c>
       <c r="AL2">
-        <v>7.225000000000001</v>
+        <v>4.263</v>
       </c>
       <c r="AM2">
-        <v>6.732</v>
+        <v>-0.109</v>
       </c>
       <c r="AN2">
-        <v>0.4136889783593357</v>
+        <v>0.1261904761904762</v>
       </c>
       <c r="AO2">
-        <v>190.7112802768166</v>
+        <v>79.14614121510674</v>
       </c>
       <c r="AP2">
-        <v>-0.2833568193256166</v>
+        <v>-0.1807738095238096</v>
       </c>
       <c r="AQ2">
-        <v>204.6775103980986</v>
+        <v>-3095.412844036698</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BBGI Global Infrastructure S.A. (LSE:BBGI)</t>
+          <t>NB Aurora S.A. SICAF-RAIF (BIT:AUR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -709,122 +721,101 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.179</v>
-      </c>
-      <c r="E3">
-        <v>0.162</v>
-      </c>
       <c r="G3">
-        <v>0.4373795761078998</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.4373795761078998</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.8636801541425819</v>
+        <v>0.8383233532934132</v>
       </c>
       <c r="J3">
-        <v>0.8464952473528387</v>
+        <v>0.8383233532934132</v>
       </c>
       <c r="K3">
-        <v>152.7</v>
+        <v>28</v>
       </c>
       <c r="L3">
-        <v>0.7355491329479769</v>
+        <v>0.8383233532934132</v>
       </c>
       <c r="M3">
-        <v>60.4</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.04487369985141159</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.39554682383759</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>60.4</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.04487369985141159</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.39554682383759</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>48.8</v>
+        <v>13.6</v>
       </c>
       <c r="V3">
-        <v>0.0362555720653789</v>
+        <v>0.03837471783295711</v>
       </c>
       <c r="W3">
-        <v>0.1204258675078864</v>
+        <v>0.09096816114359974</v>
       </c>
       <c r="X3">
-        <v>0.07265878318576451</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y3">
-        <v>0.04776708432212193</v>
+        <v>0.0286597726077981</v>
       </c>
       <c r="Z3">
-        <v>0.1648534900341459</v>
+        <v>0.1237954040029652</v>
       </c>
       <c r="AA3">
-        <v>0.1395476958234331</v>
+        <v>0.1037805782060786</v>
       </c>
       <c r="AB3">
-        <v>0.07236031322134205</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC3">
-        <v>0.06718738260209102</v>
+        <v>0.04147218967027694</v>
       </c>
       <c r="AD3">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-37.9</v>
+        <v>-13.6</v>
       </c>
       <c r="AH3">
-        <v>0.008033016434519862</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.008323787705231005</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0289733200825625</v>
+        <v>-0.03990610328638498</v>
       </c>
       <c r="AK3">
-        <v>-0.03006266359958753</v>
+        <v>-0.04048824054778208</v>
       </c>
       <c r="AL3">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>2.403</v>
-      </c>
-      <c r="AN3">
-        <v>0.06075808249721294</v>
-      </c>
-      <c r="AO3">
-        <v>74.39834024896265</v>
-      </c>
-      <c r="AP3">
-        <v>-0.2112597547380156</v>
-      </c>
-      <c r="AQ3">
-        <v>74.61506450270495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Reinet Investments S.C.A. (BDL:REINI)</t>
+          <t>Luxempart S.A. (BDL:LXMPR)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -843,74 +834,80 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.09449999999999999</v>
+      </c>
+      <c r="E4">
+        <v>-0.105</v>
+      </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.213571117877338</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.213571117877338</v>
       </c>
       <c r="I4">
-        <v>0.9934902353530296</v>
+        <v>0.8999565028273162</v>
       </c>
       <c r="J4">
-        <v>0.9934902353530296</v>
+        <v>0.8931029549714204</v>
       </c>
       <c r="K4">
-        <v>744.3</v>
+        <v>208.5</v>
       </c>
       <c r="L4">
-        <v>1.242363545317977</v>
+        <v>0.9069160504567203</v>
       </c>
       <c r="M4">
-        <v>98</v>
+        <v>44.422</v>
       </c>
       <c r="N4">
-        <v>0.02833762253130151</v>
+        <v>0.03019439912996194</v>
       </c>
       <c r="O4">
-        <v>0.1316673384388016</v>
+        <v>0.2130551558752998</v>
       </c>
       <c r="P4">
-        <v>50</v>
+        <v>43.6</v>
       </c>
       <c r="Q4">
-        <v>0.01445797067923546</v>
+        <v>0.02963567156063078</v>
       </c>
       <c r="R4">
-        <v>0.06717721348918447</v>
+        <v>0.2091127098321343</v>
       </c>
       <c r="S4">
-        <v>48</v>
+        <v>0.8220000000000027</v>
       </c>
       <c r="T4">
-        <v>0.4897959183673469</v>
+        <v>0.01850434469407056</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.027868406742795</v>
       </c>
       <c r="W4">
-        <v>0.1342920034642032</v>
+        <v>0.09600331522239616</v>
       </c>
       <c r="X4">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y4">
-        <v>0.06183778442349837</v>
+        <v>0.03369492668659453</v>
       </c>
       <c r="Z4">
-        <v>0.1080713476538542</v>
+        <v>0.1095335652008195</v>
       </c>
       <c r="AA4">
-        <v>0.1073678286155467</v>
+        <v>0.09782475074940662</v>
       </c>
       <c r="AB4">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC4">
-        <v>0.03491360957484185</v>
+        <v>0.03551636221360499</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -922,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>-41</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -931,16 +928,28 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>-0.0286673192560481</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>-0.0171089968285762</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.388</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-3.382</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>533.2474226804123</v>
+      </c>
+      <c r="AP4">
+        <v>-0.1980676328502415</v>
+      </c>
+      <c r="AQ4">
+        <v>-61.17681845062094</v>
       </c>
     </row>
     <row r="5">
@@ -960,10 +969,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.101</v>
+        <v>-0.06709999999999999</v>
       </c>
       <c r="E5">
-        <v>0.0965</v>
+        <v>-0.0542</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,34 +981,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>1.086703601108033</v>
+        <v>1.209115281501341</v>
       </c>
       <c r="J5">
-        <v>1.086703601108033</v>
+        <v>1.209041514068748</v>
       </c>
       <c r="K5">
-        <v>392.3</v>
+        <v>180.3</v>
       </c>
       <c r="L5">
-        <v>1.086703601108033</v>
+        <v>1.208445040214477</v>
       </c>
       <c r="M5">
-        <v>35.2</v>
+        <v>39</v>
       </c>
       <c r="N5">
-        <v>0.01079258010118044</v>
+        <v>0.01185014129014615</v>
       </c>
       <c r="O5">
-        <v>0.08972724955391283</v>
+        <v>0.21630615640599</v>
       </c>
       <c r="P5">
-        <v>35.2</v>
+        <v>39</v>
       </c>
       <c r="Q5">
-        <v>0.01079258010118044</v>
+        <v>0.01185014129014615</v>
       </c>
       <c r="R5">
-        <v>0.08972724955391283</v>
+        <v>0.21630615640599</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,31 +1017,31 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.125</v>
+        <v>0.055</v>
       </c>
       <c r="V5">
-        <v>3.832592365476008e-05</v>
+        <v>1.671173771687278e-05</v>
       </c>
       <c r="W5">
-        <v>0.1019490644490645</v>
+        <v>0.04808384670773663</v>
       </c>
       <c r="X5">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y5">
-        <v>0.0294948454083596</v>
+        <v>-0.01422454182806501</v>
       </c>
       <c r="Z5">
-        <v>0.09382016208277641</v>
+        <v>0.03979117633331777</v>
       </c>
       <c r="AA5">
-        <v>0.1019547079918925</v>
+        <v>0.04810918408061104</v>
       </c>
       <c r="AB5">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC5">
-        <v>0.02950048895118763</v>
+        <v>-0.01419920445519059</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1044,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-0.125</v>
+        <v>-0.055</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1053,16 +1062,22 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-3.832739258748227e-05</v>
+        <v>-1.671201700371766e-05</v>
       </c>
       <c r="AK5">
-        <v>-3.333711153930779e-05</v>
+        <v>-1.35566650111103e-05</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.055</v>
+      </c>
+      <c r="AO5">
+        <v>3280</v>
+      </c>
+      <c r="AQ5">
+        <v>3280</v>
       </c>
     </row>
     <row r="6">
@@ -1073,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Luxempart S.A. (BDL:LXMPR)</t>
+          <t>BBGI Global Infrastructure S.A. (LSE:BBGI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,121 +1097,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0269</v>
+        <v>-0.08560000000000001</v>
       </c>
       <c r="E6">
-        <v>0.0973</v>
+        <v>-0.0828</v>
       </c>
       <c r="G6">
-        <v>2.421589460263493</v>
+        <v>3.025454545454545</v>
       </c>
       <c r="H6">
-        <v>2.421589460263493</v>
+        <v>3.025454545454545</v>
       </c>
       <c r="I6">
-        <v>0.9260518487037824</v>
+        <v>0.8163636363636363</v>
       </c>
       <c r="J6">
-        <v>0.9163332278227949</v>
+        <v>0.7250158837445082</v>
       </c>
       <c r="K6">
-        <v>214.1</v>
+        <v>47.8</v>
       </c>
       <c r="L6">
-        <v>0.9099022524436888</v>
+        <v>0.869090909090909</v>
       </c>
       <c r="M6">
-        <v>37.969</v>
+        <v>65.7</v>
       </c>
       <c r="N6">
-        <v>0.02366406980367716</v>
+        <v>0.05095393206142391</v>
       </c>
       <c r="O6">
-        <v>0.1773423633815974</v>
+        <v>1.374476987447699</v>
       </c>
       <c r="P6">
-        <v>37.9</v>
+        <v>65.7</v>
       </c>
       <c r="Q6">
-        <v>0.02362106575257089</v>
+        <v>0.05095393206142391</v>
       </c>
       <c r="R6">
-        <v>0.1770200840728632</v>
+        <v>1.374476987447699</v>
       </c>
       <c r="S6">
-        <v>0.06900000000000261</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.001817271985040497</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>72.90000000000001</v>
+        <v>22.7</v>
       </c>
       <c r="V6">
-        <v>0.04543471486444375</v>
+        <v>0.01760508763766093</v>
       </c>
       <c r="W6">
-        <v>0.09462565190488818</v>
+        <v>0.03680887109194517</v>
       </c>
       <c r="X6">
-        <v>0.07245421904070486</v>
+        <v>0.06274357048603596</v>
       </c>
       <c r="Y6">
-        <v>0.02217143286418333</v>
+        <v>-0.02593469939409079</v>
       </c>
       <c r="Z6">
-        <v>0.104276534456016</v>
+        <v>0.04362655667486317</v>
       </c>
       <c r="AA6">
-        <v>0.09555205340425602</v>
+        <v>0.03162994654235579</v>
       </c>
       <c r="AB6">
-        <v>0.07245421904070486</v>
+        <v>0.06204715013255735</v>
       </c>
       <c r="AC6">
-        <v>0.02309783436355116</v>
+        <v>-0.03041720359020156</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="AG6">
-        <v>-72.90000000000001</v>
+        <v>9.100000000000001</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.02406902815622161</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.02313231977886084</v>
       </c>
       <c r="AJ6">
-        <v>-0.04759728388613216</v>
+        <v>0.007008086253369274</v>
       </c>
       <c r="AK6">
-        <v>-0.03473247891752823</v>
+        <v>0.006730769230769232</v>
       </c>
       <c r="AL6">
-        <v>0.963</v>
+        <v>3.82</v>
       </c>
       <c r="AM6">
-        <v>0.477</v>
+        <v>3.218</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="AO6">
-        <v>226.2720664589824</v>
+        <v>11.75392670157068</v>
       </c>
       <c r="AP6">
-        <v>-0.3344036697247706</v>
+        <v>0.2022222222222222</v>
       </c>
       <c r="AQ6">
-        <v>456.8134171907757</v>
+        <v>13.952765692977</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1222,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>468 SPAC II SE (DB:SPV2)</t>
+          <t>Reinet Investments S.C.A. (BDL:REINI)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1216,40 +1231,58 @@
         </is>
       </c>
       <c r="K7">
-        <v>-0.5659999999999999</v>
+        <v>243.4</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>58.2</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.01293448306516135</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>0.2391125718981101</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>58.2</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.01293448306516135</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>0.2391125718981101</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>0.01360239162929746</v>
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.04561982231885145</v>
       </c>
       <c r="X7">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="Y7">
+        <v>-0.01668856621695018</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>-0.02301608126850845</v>
       </c>
       <c r="AB7">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="AC7">
+        <v>-0.08532446980431008</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1261,381 +1294,25 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-3.64</v>
+        <v>0</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AI7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.01378996817699651</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>0.3466666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL7">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>0.001</v>
-      </c>
-      <c r="AO7">
-        <v>-564.9999999999999</v>
-      </c>
-      <c r="AQ7">
-        <v>-564.9999999999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>OboTech Acquisition SE (DB:OTA)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K8">
-        <v>-11</v>
-      </c>
-      <c r="M8">
-        <v>-0</v>
-      </c>
-      <c r="N8">
-        <v>-0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>-0</v>
-      </c>
-      <c r="Q8">
-        <v>-0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>2.05</v>
-      </c>
-      <c r="V8">
-        <v>0.007768093974990527</v>
-      </c>
-      <c r="X8">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AB8">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>-2.05</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>-0</v>
-      </c>
-      <c r="AJ8">
-        <v>-0.007828909681115142</v>
-      </c>
-      <c r="AK8">
-        <v>0.1734348561759729</v>
-      </c>
-      <c r="AL8">
-        <v>3.81</v>
-      </c>
-      <c r="AM8">
-        <v>3.81</v>
-      </c>
-      <c r="AO8">
-        <v>-0.5013123359580052</v>
-      </c>
-      <c r="AQ8">
-        <v>-0.5013123359580052</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GFJ ESG Acquisition I SE (DB:GFJ1)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K9">
-        <v>-16.8</v>
-      </c>
-      <c r="M9">
-        <v>-0</v>
-      </c>
-      <c r="N9">
-        <v>-0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>-0</v>
-      </c>
-      <c r="Q9">
-        <v>-0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0.131</v>
-      </c>
-      <c r="V9">
-        <v>0.0006569709127382146</v>
-      </c>
-      <c r="X9">
-        <v>0.09190026478110001</v>
-      </c>
-      <c r="AB9">
-        <v>0.07112405292533676</v>
-      </c>
-      <c r="AD9">
-        <v>153.5</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>153.5</v>
-      </c>
-      <c r="AG9">
-        <v>153.369</v>
-      </c>
-      <c r="AH9">
-        <v>0.4349674128648343</v>
-      </c>
-      <c r="AI9">
-        <v>1.083274523641496</v>
-      </c>
-      <c r="AJ9">
-        <v>0.4347575892439529</v>
-      </c>
-      <c r="AK9">
-        <v>1.08335158120775</v>
-      </c>
-      <c r="AL9">
-        <v>0.04</v>
-      </c>
-      <c r="AM9">
-        <v>0.04</v>
-      </c>
-      <c r="AO9">
-        <v>-43</v>
-      </c>
-      <c r="AQ9">
-        <v>-43</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Hiro Metaverse Acquisitions I S.A. (LSE:HMA1)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K10">
-        <v>-0.825</v>
-      </c>
-      <c r="M10">
-        <v>-0</v>
-      </c>
-      <c r="N10">
-        <v>-0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>-0</v>
-      </c>
-      <c r="Q10">
-        <v>-0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>146.8</v>
-      </c>
-      <c r="V10">
-        <v>0.8256467941507312</v>
-      </c>
-      <c r="X10">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AB10">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <v>-146.8</v>
-      </c>
-      <c r="AH10">
-        <v>0</v>
-      </c>
-      <c r="AI10">
-        <v>0</v>
-      </c>
-      <c r="AJ10">
-        <v>-4.735483870967743</v>
-      </c>
-      <c r="AK10">
-        <v>1.002458344714559</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SMG European Recovery SPAC SE (DB:RCVR)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K11">
-        <v>-1.79</v>
-      </c>
-      <c r="M11">
-        <v>-0</v>
-      </c>
-      <c r="N11">
-        <v>-0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>-0</v>
-      </c>
-      <c r="Q11">
-        <v>-0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>2.56</v>
-      </c>
-      <c r="V11">
-        <v>0.01649484536082474</v>
-      </c>
-      <c r="X11">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AB11">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>-2.56</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>-0</v>
-      </c>
-      <c r="AJ11">
-        <v>-0.01677148846960168</v>
-      </c>
-      <c r="AK11">
-        <v>0.4942084942084942</v>
-      </c>
-      <c r="AL11">
-        <v>0.001</v>
-      </c>
-      <c r="AM11">
-        <v>0.001</v>
-      </c>
-      <c r="AO11">
-        <v>-1790</v>
-      </c>
-      <c r="AQ11">
-        <v>-1790</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
